--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-signes-vital-Observe-document.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-signes-vital-Observe-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,9 +85,9 @@
   </si>
   <si>
     <t xml:space="preserve">
- - Cette entrée permet d'indiquer les informations détaillées relatives à une mesure clinique spécifique.
- - Cette entrée est utilisée dans un élément component d'un élément Signes vitaux (1.3.6.1.4.1.19376.1.5.3.1.4.13.1).
- - Cette entrée est basée sur l'élément Simple Observation (1.3.6.1.4.1.19376.1.5.3.1.4.13) qu'elle spécialise en portant des contraintes sur les vocabulaires des éléments 'code' et 'value'.</t>
+ - FrSigneVitalObserveDocument permet d'indiquer les informations détaillées relatives à une mesure clinique spécifique.
+ - Ce profil est utilisée dans un profil FrSignesVitauxDocument.
+ - Il est basée sur la ressource Observation qu'elle spécialise en portant des contraintes sur les vocabulaires des éléments 'code' et 'value'.</t>
   </si>
   <si>
     <t>Purpose</t>
